--- a/artfynd/A 25306-2026 artfynd.xlsx
+++ b/artfynd/A 25306-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1369,32 +1369,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134360563</v>
+        <v>137340106</v>
       </c>
       <c r="B8" t="n">
-        <v>58698</v>
+        <v>58189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103055</v>
+        <v>103023</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1402,23 +1402,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dåstorp, Srm</t>
+          <t>Långängen, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>659898</v>
       </c>
       <c r="R8" t="n">
-        <v>6556665</v>
+        <v>6556763</v>
       </c>
       <c r="S8" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,22 +1440,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,27 +1460,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134360563</t>
+          <t>https://artportalen.se/Sighting/137340106</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135445379</v>
+        <v>137340431</v>
       </c>
       <c r="B9" t="n">
-        <v>8463</v>
+        <v>58189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,34 +1488,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långängen, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>659909</v>
+        <v>659790</v>
       </c>
       <c r="R9" t="n">
-        <v>6556716</v>
+        <v>6556741</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1554,12 +1548,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,22 +1573,22 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445379</t>
+          <t>https://artportalen.se/Sighting/137340431</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135445367</v>
+        <v>134360563</v>
       </c>
       <c r="B10" t="n">
-        <v>110009</v>
+        <v>58698</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,49 +1596,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220204</v>
+        <v>103055</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långängen, Srm</t>
+          <t>Dåstorp, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>659914</v>
+        <v>659898</v>
       </c>
       <c r="R10" t="n">
-        <v>6556664</v>
+        <v>6556665</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,12 +1658,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,69 +1682,74 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445367</t>
+          <t>https://artportalen.se/Sighting/134360563</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135445386</v>
+        <v>137340290</v>
       </c>
       <c r="B11" t="n">
-        <v>99570</v>
+        <v>58756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222812</v>
+        <v>103055</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kvarnbacken, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>659905</v>
+        <v>659925</v>
       </c>
       <c r="R11" t="n">
-        <v>6556635</v>
+        <v>6556645</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1771,12 +1776,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,57 +1801,63 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445386</t>
+          <t>https://artportalen.se/Sighting/137340290</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135445383</v>
+        <v>137340397</v>
       </c>
       <c r="B12" t="n">
-        <v>96505</v>
+        <v>58756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2812</v>
+        <v>103055</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långängen, Srm</t>
+          <t>Kvarnbacken, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>659976</v>
+        <v>659894</v>
       </c>
       <c r="R12" t="n">
-        <v>6556823</v>
+        <v>6556609</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1873,12 +1884,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1898,44 +1909,44 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445383</t>
+          <t>https://artportalen.se/Sighting/137340397</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134360551</v>
+        <v>137340472</v>
       </c>
       <c r="B13" t="n">
-        <v>57972</v>
+        <v>58756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103055</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1943,23 +1954,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Dåstorp, Dåstorp, Srm</t>
+          <t>Kvarnbacken, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>659935</v>
+        <v>659905</v>
       </c>
       <c r="R13" t="n">
-        <v>6556806</v>
+        <v>6556635</v>
       </c>
       <c r="S13" t="n">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1983,22 +1992,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2013,27 +2012,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134360551</t>
+          <t>https://artportalen.se/Sighting/137340472</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135445369</v>
+        <v>135445379</v>
       </c>
       <c r="B14" t="n">
-        <v>58138</v>
+        <v>8463</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2041,21 +2040,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103023</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2065,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>659970</v>
+        <v>659909</v>
       </c>
       <c r="R14" t="n">
-        <v>6556790</v>
+        <v>6556716</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,33 +2125,33 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445369</t>
+          <t>https://artportalen.se/Sighting/135445379</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135445384</v>
+        <v>135445367</v>
       </c>
       <c r="B15" t="n">
-        <v>99570</v>
+        <v>110009</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222812</v>
+        <v>220204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2160,17 +2159,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långängen, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>659986</v>
+        <v>659914</v>
       </c>
       <c r="R15" t="n">
-        <v>6556878</v>
+        <v>6556664</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2197,12 +2208,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2211,6 +2222,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2222,11 +2234,1190 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445367</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135445386</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99570</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kvarnbacken, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>659905</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6556635</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445386</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135445383</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96505</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>659976</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6556823</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445383</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134360551</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Dåstorp, Dåstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>659935</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6556806</v>
+      </c>
+      <c r="S18" t="n">
+        <v>68</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134360551</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137340393</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58468</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>659985</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6556785</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137340393</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137340202</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58318</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>660044</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6556819</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137340202</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135445369</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58138</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>659970</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6556790</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445369</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137340336</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58433</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>660017</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6556788</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137340336</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137340178</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58756</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>660051</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6556779</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137340178</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137340338</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58756</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>660024</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6556761</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137340338</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137340460</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58756</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>660014</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6556722</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137340460</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135445384</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99570</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>659986</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6556878</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135445384</t>
         </is>
@@ -2248,6 +3439,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25306-2026 artfynd.xlsx
+++ b/artfynd/A 25306-2026 artfynd.xlsx
@@ -1372,7 +1372,7 @@
         <v>137340106</v>
       </c>
       <c r="B8" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>137340431</v>
       </c>
       <c r="B9" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137340290</v>
       </c>
       <c r="B11" t="n">
-        <v>58756</v>
+        <v>58758</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>137340397</v>
       </c>
       <c r="B12" t="n">
-        <v>58756</v>
+        <v>58758</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>137340472</v>
       </c>
       <c r="B13" t="n">
-        <v>58756</v>
+        <v>58758</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>137340393</v>
       </c>
       <c r="B19" t="n">
-        <v>58468</v>
+        <v>58469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>137340202</v>
       </c>
       <c r="B20" t="n">
-        <v>58318</v>
+        <v>58319</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>137340336</v>
       </c>
       <c r="B22" t="n">
-        <v>58433</v>
+        <v>58434</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>137340178</v>
       </c>
       <c r="B23" t="n">
-        <v>58756</v>
+        <v>58758</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>137340338</v>
       </c>
       <c r="B24" t="n">
-        <v>58756</v>
+        <v>58758</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>137340460</v>
       </c>
       <c r="B25" t="n">
-        <v>58756</v>
+        <v>58758</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 25306-2026 artfynd.xlsx
+++ b/artfynd/A 25306-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ26"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1249,32 +1249,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134360549</v>
+        <v>137397654</v>
       </c>
       <c r="B7" t="n">
-        <v>57969</v>
+        <v>56905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102977</v>
+        <v>100087</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1282,23 +1282,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dåstorp, Srm</t>
+          <t>Dalsta, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>659898</v>
+        <v>659797</v>
       </c>
       <c r="R7" t="n">
-        <v>6556665</v>
+        <v>6556723</v>
       </c>
       <c r="S7" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,22 +1318,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:23</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Autobox: 6b</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,68 +1343,66 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134360549</t>
+          <t>https://artportalen.se/Sighting/137397654</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137340106</v>
+        <v>137397683</v>
       </c>
       <c r="B8" t="n">
-        <v>58190</v>
+        <v>56905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103023</v>
+        <v>100087</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långängen, Srm</t>
+          <t>Dalsta, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>659898</v>
+        <v>659912</v>
       </c>
       <c r="R8" t="n">
-        <v>6556763</v>
+        <v>6556779</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1440,12 +1429,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Autobox: 9a</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,7 +1454,7 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1471,16 +1465,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137340106</t>
+          <t>https://artportalen.se/Sighting/137397683</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137340431</v>
+        <v>137397634</v>
       </c>
       <c r="B9" t="n">
-        <v>58190</v>
+        <v>56908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,21 +1482,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103023</v>
+        <v>100092</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1510,18 +1504,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långängen, Srm</t>
+          <t>Dalsta, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>659790</v>
+        <v>659797</v>
       </c>
       <c r="R9" t="n">
-        <v>6556741</v>
+        <v>6556716</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1548,12 +1540,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,7 +1560,7 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -1579,62 +1571,58 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137340431</t>
+          <t>https://artportalen.se/Sighting/137397634</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134360563</v>
+        <v>137397650</v>
       </c>
       <c r="B10" t="n">
-        <v>58698</v>
+        <v>56908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103055</v>
+        <v>100092</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dåstorp, Srm</t>
+          <t>Dalsta, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>659898</v>
+        <v>659902</v>
       </c>
       <c r="R10" t="n">
-        <v>6556665</v>
+        <v>6556723</v>
       </c>
       <c r="S10" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1658,22 +1646,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:09</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Autobox: 7b</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,68 +1671,66 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134360563</t>
+          <t>https://artportalen.se/Sighting/137397650</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137340290</v>
+        <v>137397655</v>
       </c>
       <c r="B11" t="n">
-        <v>58758</v>
+        <v>56908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103055</v>
+        <v>100092</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kvarnbacken, Srm</t>
+          <t>Dalsta, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>659925</v>
+        <v>659797</v>
       </c>
       <c r="R11" t="n">
-        <v>6556645</v>
+        <v>6556723</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1776,12 +1757,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Autobox: 6b</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,7 +1782,7 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -1807,57 +1793,55 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137340290</t>
+          <t>https://artportalen.se/Sighting/137397655</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137340397</v>
+        <v>137397684</v>
       </c>
       <c r="B12" t="n">
-        <v>58758</v>
+        <v>56908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103055</v>
+        <v>100092</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kvarnbacken, Srm</t>
+          <t>Dalsta, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>659894</v>
+        <v>659912</v>
       </c>
       <c r="R12" t="n">
-        <v>6556609</v>
+        <v>6556779</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1884,12 +1868,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Autobox: 9a</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1904,7 +1893,7 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -1915,57 +1904,55 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137340397</t>
+          <t>https://artportalen.se/Sighting/137397684</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137340472</v>
+        <v>137397688</v>
       </c>
       <c r="B13" t="n">
-        <v>58758</v>
+        <v>56908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103055</v>
+        <v>100092</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>36</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kvarnbacken, Srm</t>
+          <t>Dalsta, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>659905</v>
+        <v>659806</v>
       </c>
       <c r="R13" t="n">
-        <v>6556635</v>
+        <v>6556657</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1992,12 +1979,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Autobox: 8a</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,7 +2004,7 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -2023,16 +2015,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137340472</t>
+          <t>https://artportalen.se/Sighting/137397688</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135445379</v>
+        <v>134360549</v>
       </c>
       <c r="B14" t="n">
-        <v>8463</v>
+        <v>57969</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,37 +2032,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>102977</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långängen, Srm</t>
+          <t>Dåstorp, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>659909</v>
+        <v>659898</v>
       </c>
       <c r="R14" t="n">
-        <v>6556716</v>
+        <v>6556665</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2094,12 +2094,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,63 +2124,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445379</t>
+          <t>https://artportalen.se/Sighting/134360549</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135445367</v>
+        <v>137340106</v>
       </c>
       <c r="B15" t="n">
-        <v>110009</v>
+        <v>58191</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220204</v>
+        <v>103023</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2178,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>659914</v>
+        <v>659898</v>
       </c>
       <c r="R15" t="n">
-        <v>6556664</v>
+        <v>6556763</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2208,12 +2212,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2222,7 +2226,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2234,22 +2237,22 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445367</t>
+          <t>https://artportalen.se/Sighting/137340106</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135445386</v>
+        <v>137340431</v>
       </c>
       <c r="B16" t="n">
-        <v>99570</v>
+        <v>58191</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2257,34 +2260,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222812</v>
+        <v>103023</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kvarnbacken, Srm</t>
+          <t>Långängen, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>659905</v>
+        <v>659790</v>
       </c>
       <c r="R16" t="n">
-        <v>6556635</v>
+        <v>6556741</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2311,12 +2320,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2336,60 +2345,68 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445386</t>
+          <t>https://artportalen.se/Sighting/137340431</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135445383</v>
+        <v>134360563</v>
       </c>
       <c r="B17" t="n">
-        <v>96505</v>
+        <v>58698</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2812</v>
+        <v>103055</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långängen, Srm</t>
+          <t>Dåstorp, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>659976</v>
+        <v>659898</v>
       </c>
       <c r="R17" t="n">
-        <v>6556823</v>
+        <v>6556665</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2413,12 +2430,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2433,49 +2460,49 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445383</t>
+          <t>https://artportalen.se/Sighting/134360563</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134360551</v>
+        <v>137340290</v>
       </c>
       <c r="B18" t="n">
-        <v>57972</v>
+        <v>58760</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>103055</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2483,23 +2510,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Dåstorp, Dåstorp, Srm</t>
+          <t>Kvarnbacken, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>659935</v>
+        <v>659925</v>
       </c>
       <c r="R18" t="n">
-        <v>6556806</v>
+        <v>6556645</v>
       </c>
       <c r="S18" t="n">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2523,22 +2548,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2553,27 +2568,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134360551</t>
+          <t>https://artportalen.se/Sighting/137340290</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137340393</v>
+        <v>137340397</v>
       </c>
       <c r="B19" t="n">
-        <v>58469</v>
+        <v>58760</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2581,21 +2596,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103001</v>
+        <v>103055</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2607,14 +2622,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långängen, Srm</t>
+          <t>Kvarnbacken, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>659985</v>
+        <v>659894</v>
       </c>
       <c r="R19" t="n">
-        <v>6556785</v>
+        <v>6556609</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2672,16 +2687,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137340393</t>
+          <t>https://artportalen.se/Sighting/137340397</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137340202</v>
+        <v>137340472</v>
       </c>
       <c r="B20" t="n">
-        <v>58319</v>
+        <v>58760</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,21 +2704,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103012</v>
+        <v>103055</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2711,23 +2726,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långängen, Srm</t>
+          <t>Kvarnbacken, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>660044</v>
+        <v>659905</v>
       </c>
       <c r="R20" t="n">
-        <v>6556819</v>
+        <v>6556635</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2751,12 +2764,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2776,22 +2789,22 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137340202</t>
+          <t>https://artportalen.se/Sighting/137340472</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135445369</v>
+        <v>135445379</v>
       </c>
       <c r="B21" t="n">
-        <v>58138</v>
+        <v>8463</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2799,21 +2812,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103023</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2823,10 +2836,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>659970</v>
+        <v>659909</v>
       </c>
       <c r="R21" t="n">
-        <v>6556790</v>
+        <v>6556716</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2884,58 +2897,55 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445369</t>
+          <t>https://artportalen.se/Sighting/135445379</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137340336</v>
+        <v>137397635</v>
       </c>
       <c r="B22" t="n">
-        <v>58434</v>
+        <v>56901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103037</v>
+        <v>205992</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långängen, Srm</t>
+          <t>Dalsta, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>660017</v>
+        <v>659914</v>
       </c>
       <c r="R22" t="n">
-        <v>6556788</v>
+        <v>6556775</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2962,12 +2972,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Minst 4 ex runt den lilla pölen, samma art som punkten strax öster om</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2982,7 +2997,7 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -2993,38 +3008,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137340336</t>
+          <t>https://artportalen.se/Sighting/137397635</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137340178</v>
+        <v>137397653</v>
       </c>
       <c r="B23" t="n">
-        <v>58758</v>
+        <v>56901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103055</v>
+        <v>205992</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3032,18 +3047,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långängen, Srm</t>
+          <t>Dalsta, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>660051</v>
+        <v>659797</v>
       </c>
       <c r="R23" t="n">
-        <v>6556779</v>
+        <v>6556723</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3070,12 +3083,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Autobox: 6b</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3090,7 +3108,7 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -3101,57 +3119,55 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137340178</t>
+          <t>https://artportalen.se/Sighting/137397653</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137340338</v>
+        <v>137397682</v>
       </c>
       <c r="B24" t="n">
-        <v>58758</v>
+        <v>56901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103055</v>
+        <v>205992</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>149</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långängen, Srm</t>
+          <t>Dalsta, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>660024</v>
+        <v>659912</v>
       </c>
       <c r="R24" t="n">
-        <v>6556761</v>
+        <v>6556779</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3178,12 +3194,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Autobox: 9a</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3198,7 +3219,7 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -3209,57 +3230,55 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137340338</t>
+          <t>https://artportalen.se/Sighting/137397682</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137340460</v>
+        <v>137397687</v>
       </c>
       <c r="B25" t="n">
-        <v>58758</v>
+        <v>56901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103055</v>
+        <v>205992</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långängen, Srm</t>
+          <t>Dalsta, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>660014</v>
+        <v>659806</v>
       </c>
       <c r="R25" t="n">
-        <v>6556722</v>
+        <v>6556657</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3286,12 +3305,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Autobox: 8a</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3306,7 +3330,7 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -3317,16 +3341,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137340460</t>
+          <t>https://artportalen.se/Sighting/137397687</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135445384</v>
+        <v>137397652</v>
       </c>
       <c r="B26" t="n">
-        <v>99570</v>
+        <v>56913</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3334,34 +3358,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222812</v>
+        <v>205995</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långängen, Srm</t>
+          <t>Dalsta, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>659986</v>
+        <v>659902</v>
       </c>
       <c r="R26" t="n">
-        <v>6556878</v>
+        <v>6556723</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3388,12 +3416,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Autobox: 7b</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3408,16 +3441,2843 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137397652</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137397658</v>
+      </c>
+      <c r="B27" t="n">
+        <v>56913</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Dalsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>659797</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6556723</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Autobox: 6b</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137397658</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137397686</v>
+      </c>
+      <c r="B28" t="n">
+        <v>56913</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Dalsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>659912</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6556779</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Autobox: 9a</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137397686</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137397692</v>
+      </c>
+      <c r="B29" t="n">
+        <v>56913</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Dalsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>659806</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6556657</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Autobox: 8a</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137397692</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137397657</v>
+      </c>
+      <c r="B30" t="n">
+        <v>56892</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Dalsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>659797</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6556723</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Autobox: 6b</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137397657</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137397691</v>
+      </c>
+      <c r="B31" t="n">
+        <v>56892</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Dalsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>659806</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6556657</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Autobox: 8a</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137397691</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135445367</v>
+      </c>
+      <c r="B32" t="n">
+        <v>110009</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>659914</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6556664</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445367</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135445386</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99570</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kvarnbacken, Srm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>659905</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6556635</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445386</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135445383</v>
+      </c>
+      <c r="B34" t="n">
+        <v>96505</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>659976</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6556823</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445383</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134360551</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Dåstorp, Dåstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>659935</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6556806</v>
+      </c>
+      <c r="S35" t="n">
+        <v>68</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134360551</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137397637</v>
+      </c>
+      <c r="B36" t="n">
+        <v>56908</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Dalsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>659970</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6556790</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137397637</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137397638</v>
+      </c>
+      <c r="B37" t="n">
+        <v>56908</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Dalsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>659969</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6556861</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Autobox: 9b</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137397638</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137397644</v>
+      </c>
+      <c r="B38" t="n">
+        <v>56908</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Dalsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>659956</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6556751</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Autobox: 8b</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137397644</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>137340393</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58471</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>659985</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6556785</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137340393</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>137340202</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58321</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>660044</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6556819</v>
+      </c>
+      <c r="S40" t="n">
+        <v>20</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137340202</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135445369</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58138</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>659970</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6556790</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445369</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>137340336</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58436</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>660017</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6556788</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137340336</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>137340178</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58760</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>660051</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6556779</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137340178</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137340338</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58760</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>660024</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6556761</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137340338</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>137340460</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58760</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>660014</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6556722</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137340460</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>137397636</v>
+      </c>
+      <c r="B46" t="n">
+        <v>56901</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Dalsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>659963</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6556792</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Fladdermus sedd, flera inspelningar, 2 meters höjd 22:50</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137397636</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>137397643</v>
+      </c>
+      <c r="B47" t="n">
+        <v>56901</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Dalsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>659956</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6556751</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Autobox: 8b</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137397643</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>137397641</v>
+      </c>
+      <c r="B48" t="n">
+        <v>56913</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Dalsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>659969</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6556861</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Autobox: 9b</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137397641</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>137397648</v>
+      </c>
+      <c r="B49" t="n">
+        <v>56913</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Dalsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>659956</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6556751</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Autobox: 8b</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137397648</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>137397640</v>
+      </c>
+      <c r="B50" t="n">
+        <v>56892</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Dalsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>659969</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6556861</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Autobox: 9b</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137397640</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>137397646</v>
+      </c>
+      <c r="B51" t="n">
+        <v>56892</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Dalsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>659956</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6556751</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Autobox: 8b</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137397646</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135445384</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99570</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>659986</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6556878</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135445384</t>
         </is>
@@ -3450,6 +6310,32 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25306-2026 artfynd.xlsx
+++ b/artfynd/A 25306-2026 artfynd.xlsx
@@ -1252,7 +1252,7 @@
         <v>137397654</v>
       </c>
       <c r="B7" t="n">
-        <v>56905</v>
+        <v>56908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>137397683</v>
       </c>
       <c r="B8" t="n">
-        <v>56905</v>
+        <v>56908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>137397634</v>
       </c>
       <c r="B9" t="n">
-        <v>56908</v>
+        <v>56911</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>137397650</v>
       </c>
       <c r="B10" t="n">
-        <v>56908</v>
+        <v>56911</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137397655</v>
       </c>
       <c r="B11" t="n">
-        <v>56908</v>
+        <v>56911</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>137397684</v>
       </c>
       <c r="B12" t="n">
-        <v>56908</v>
+        <v>56911</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>137397688</v>
       </c>
       <c r="B13" t="n">
-        <v>56908</v>
+        <v>56911</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137340106</v>
       </c>
       <c r="B15" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>137340431</v>
       </c>
       <c r="B16" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>137340290</v>
       </c>
       <c r="B18" t="n">
-        <v>58760</v>
+        <v>58763</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>137340397</v>
       </c>
       <c r="B19" t="n">
-        <v>58760</v>
+        <v>58763</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>137340472</v>
       </c>
       <c r="B20" t="n">
-        <v>58760</v>
+        <v>58763</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>137397635</v>
       </c>
       <c r="B22" t="n">
-        <v>56901</v>
+        <v>56904</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>137397653</v>
       </c>
       <c r="B23" t="n">
-        <v>56901</v>
+        <v>56904</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>137397682</v>
       </c>
       <c r="B24" t="n">
-        <v>56901</v>
+        <v>56904</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>137397687</v>
       </c>
       <c r="B25" t="n">
-        <v>56901</v>
+        <v>56904</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>137397652</v>
       </c>
       <c r="B26" t="n">
-        <v>56913</v>
+        <v>56916</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>137397658</v>
       </c>
       <c r="B27" t="n">
-        <v>56913</v>
+        <v>56916</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>137397686</v>
       </c>
       <c r="B28" t="n">
-        <v>56913</v>
+        <v>56916</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>137397692</v>
       </c>
       <c r="B29" t="n">
-        <v>56913</v>
+        <v>56916</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>137397657</v>
       </c>
       <c r="B30" t="n">
-        <v>56892</v>
+        <v>56895</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>137397691</v>
       </c>
       <c r="B31" t="n">
-        <v>56892</v>
+        <v>56895</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>137397637</v>
       </c>
       <c r="B36" t="n">
-        <v>56908</v>
+        <v>56911</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>137397638</v>
       </c>
       <c r="B37" t="n">
-        <v>56908</v>
+        <v>56911</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>137397644</v>
       </c>
       <c r="B38" t="n">
-        <v>56908</v>
+        <v>56911</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>137340393</v>
       </c>
       <c r="B39" t="n">
-        <v>58471</v>
+        <v>58474</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>137340202</v>
       </c>
       <c r="B40" t="n">
-        <v>58321</v>
+        <v>58324</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>137340336</v>
       </c>
       <c r="B42" t="n">
-        <v>58436</v>
+        <v>58439</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>137340178</v>
       </c>
       <c r="B43" t="n">
-        <v>58760</v>
+        <v>58763</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>137340338</v>
       </c>
       <c r="B44" t="n">
-        <v>58760</v>
+        <v>58763</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>137340460</v>
       </c>
       <c r="B45" t="n">
-        <v>58760</v>
+        <v>58763</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>137397636</v>
       </c>
       <c r="B46" t="n">
-        <v>56901</v>
+        <v>56904</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>137397643</v>
       </c>
       <c r="B47" t="n">
-        <v>56901</v>
+        <v>56904</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>137397641</v>
       </c>
       <c r="B48" t="n">
-        <v>56913</v>
+        <v>56916</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>137397648</v>
       </c>
       <c r="B49" t="n">
-        <v>56913</v>
+        <v>56916</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>137397640</v>
       </c>
       <c r="B50" t="n">
-        <v>56892</v>
+        <v>56895</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>137397646</v>
       </c>
       <c r="B51" t="n">
-        <v>56892</v>
+        <v>56895</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
